--- a/data/trans_camb/POLIPATOLOGIA_5-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,33</t>
+          <t>-0,34; 3,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,75</t>
+          <t>-0,08; 3,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 10,31</t>
+          <t>5,39; 10,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,64</t>
+          <t>3,16; 8,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,3</t>
+          <t>4,63; 9,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 15,98</t>
+          <t>9,44; 15,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,21</t>
+          <t>2,11; 5,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,09</t>
+          <t>2,76; 6,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 12,5</t>
+          <t>8,83; 12,74</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 200,23</t>
+          <t>-12,15; 178,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 203,69</t>
+          <t>-5,81; 210,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>158,0; 625,38</t>
+          <t>153,05; 582,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,6; 302,08</t>
+          <t>61,8; 296,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,58; 355,97</t>
+          <t>95,29; 375,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>197,49; 587,86</t>
+          <t>202,36; 586,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,92; 205,71</t>
+          <t>53,58; 210,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,8; 242,21</t>
+          <t>69,94; 244,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>223,52; 520,66</t>
+          <t>227,18; 525,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,69</t>
+          <t>-1,98; 1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,09</t>
+          <t>-2,32; 1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,45</t>
+          <t>-1,0; 5,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,58</t>
+          <t>0,77; 5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,62</t>
+          <t>0,7; 5,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,62</t>
+          <t>7,65; 12,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,02</t>
+          <t>0,11; 3,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,7</t>
+          <t>-0,2; 2,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,85</t>
+          <t>2,11; 7,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 59,06</t>
+          <t>-40,54; 58,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 37,78</t>
+          <t>-49,19; 37,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 174,69</t>
+          <t>-15,26; 169,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 110,18</t>
+          <t>12,41; 124,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 117,96</t>
+          <t>9,47; 115,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>105,39; 274,68</t>
+          <t>101,65; 272,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 74,66</t>
+          <t>2,46; 73,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 67,56</t>
+          <t>-3,88; 65,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,45; 191,73</t>
+          <t>45,45; 187,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,4</t>
+          <t>-1,89; 2,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,73</t>
+          <t>-2,2; 1,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,03</t>
+          <t>1,52; 6,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,31</t>
+          <t>-4,0; 2,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,5</t>
+          <t>-4,67; 1,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 54,3</t>
+          <t>3,06; 55,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,64</t>
+          <t>-2,09; 1,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,94</t>
+          <t>-2,75; 1,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 40,82</t>
+          <t>3,27; 39,87</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 98,83</t>
+          <t>-40,66; 99,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 79,84</t>
+          <t>-47,45; 76,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,89; 231,2</t>
+          <t>29,58; 262,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 26,44</t>
+          <t>-34,66; 27,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 18,4</t>
+          <t>-38,86; 16,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,19; 584,29</t>
+          <t>28,18; 690,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 27,17</t>
+          <t>-26,72; 32,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 17,61</t>
+          <t>-34,93; 17,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,98; 784,56</t>
+          <t>44,84; 660,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,89</t>
+          <t>-1,53; 1,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,4</t>
+          <t>-1,86; 1,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,67</t>
+          <t>2,77; 6,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,69</t>
+          <t>1,72; 6,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,27</t>
+          <t>1,15; 6,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,53</t>
+          <t>6,24; 13,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,91</t>
+          <t>0,71; 4,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,84</t>
+          <t>0,35; 3,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,26</t>
+          <t>5,55; 9,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 63,66</t>
+          <t>-34,64; 68,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,82; 46,4</t>
+          <t>-40,83; 51,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56,73; 229,28</t>
+          <t>57,27; 236,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,29; 111,07</t>
+          <t>20,62; 108,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,78; 104,4</t>
+          <t>13,51; 103,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,46; 206,76</t>
+          <t>78,37; 219,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,04; 79,46</t>
+          <t>11,18; 85,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,79; 78,62</t>
+          <t>5,75; 73,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88,79; 186,34</t>
+          <t>91,68; 190,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,28</t>
+          <t>-0,56; 1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,95</t>
+          <t>-0,78; 1,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,77</t>
+          <t>2,78; 5,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,41</t>
+          <t>1,87; 4,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,49</t>
+          <t>1,81; 4,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,92; 29,05</t>
+          <t>8,93; 28,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,59</t>
+          <t>0,95; 2,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,41</t>
+          <t>0,82; 2,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 18,45</t>
+          <t>6,57; 17,29</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 44,02</t>
+          <t>-15,15; 45,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 30,97</t>
+          <t>-20,25; 34,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78,76; 191,5</t>
+          <t>78,94; 196,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24,02; 71,98</t>
+          <t>25,54; 75,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,43; 73,04</t>
+          <t>23,98; 74,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>127,37; 449,22</t>
+          <t>128,89; 452,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,33; 54,18</t>
+          <t>16,94; 56,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13,87; 51,36</t>
+          <t>14,34; 51,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>124,87; 367,06</t>
+          <t>126,3; 341,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_5-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,82</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,08</t>
+          <t>13,93</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,67</t>
+          <t>10,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,23</t>
+          <t>-0,53; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,66</t>
+          <t>-0,1; 3,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,2</t>
+          <t>5,0; 9,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,54</t>
+          <t>3,15; 8,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,99</t>
+          <t>4,39; 10,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 15,77</t>
+          <t>11,37; 16,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,35</t>
+          <t>2,11; 5,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,15</t>
+          <t>2,86; 6,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,74</t>
+          <t>9,01; 12,63</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>312,5%</t>
+          <t>301,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>347,0%</t>
+          <t>369,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>340,49%</t>
+          <t>346,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 178,73</t>
+          <t>-18,88; 184,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 210,65</t>
+          <t>-4,35; 226,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153,05; 582,02</t>
+          <t>146,47; 568,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,8; 296,94</t>
+          <t>59,77; 309,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,29; 375,03</t>
+          <t>85,76; 357,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>202,36; 586,72</t>
+          <t>209,8; 608,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,58; 210,4</t>
+          <t>55,38; 207,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,94; 244,5</t>
+          <t>75,73; 260,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>227,18; 525,39</t>
+          <t>224,45; 527,65</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>7,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,66</t>
+          <t>-1,74; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,04</t>
+          <t>-2,18; 1,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,29</t>
+          <t>2,49; 6,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,56</t>
+          <t>0,92; 5,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,6</t>
+          <t>0,59; 5,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,37</t>
+          <t>7,15; 11,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,03</t>
+          <t>0,17; 3,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,79</t>
+          <t>-0,3; 2,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,9</t>
+          <t>5,39; 8,65</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>120,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>169,52%</t>
+          <t>162,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>123,63%</t>
+          <t>147,26%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 58,56</t>
+          <t>-37,27; 50,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 37,52</t>
+          <t>-46,57; 34,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 169,87</t>
+          <t>53,33; 231,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 124,62</t>
+          <t>13,04; 129,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 115,68</t>
+          <t>8,45; 115,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>101,65; 272,79</t>
+          <t>97,48; 250,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 73,37</t>
+          <t>2,7; 80,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 65,55</t>
+          <t>-5,65; 67,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,45; 187,91</t>
+          <t>94,74; 217,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,81</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,17</t>
+          <t>4,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,46</t>
+          <t>-1,76; 2,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,77</t>
+          <t>-2,29; 1,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,44</t>
+          <t>1,47; 6,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,23</t>
+          <t>-4,23; 1,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,4</t>
+          <t>-4,99; 1,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 55,84</t>
+          <t>1,38; 7,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,82</t>
+          <t>-2,05; 1,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,01</t>
+          <t>-2,93; 0,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 39,87</t>
+          <t>2,11; 6,08</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114,66%</t>
+          <t>111,46%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>223,38%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>221,1%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 99,55</t>
+          <t>-38,8; 114,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 76,87</t>
+          <t>-50,45; 74,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,58; 262,35</t>
+          <t>30,4; 250,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 27,13</t>
+          <t>-35,19; 23,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 16,99</t>
+          <t>-41,0; 16,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,18; 690,07</t>
+          <t>11,55; 86,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 32,48</t>
+          <t>-26,96; 27,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 17,11</t>
+          <t>-36,9; 15,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,84; 660,64</t>
+          <t>25,39; 105,31</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>10,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>7,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,98</t>
+          <t>-1,61; 2,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,58</t>
+          <t>-1,74; 1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,82</t>
+          <t>2,67; 6,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,8</t>
+          <t>1,52; 6,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,35</t>
+          <t>1,16; 6,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,15</t>
+          <t>8,2; 13,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,14</t>
+          <t>0,63; 3,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,66</t>
+          <t>0,37; 3,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,21</t>
+          <t>6,27; 9,54</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125,76%</t>
+          <t>122,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>138,93%</t>
+          <t>148,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>137,33%</t>
+          <t>141,05%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 68,91</t>
+          <t>-36,23; 71,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 51,37</t>
+          <t>-39,37; 53,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57,27; 236,81</t>
+          <t>57,37; 218,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,62; 108,36</t>
+          <t>18,91; 112,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,51; 103,17</t>
+          <t>14,18; 109,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,37; 219,05</t>
+          <t>99,61; 220,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,18; 85,11</t>
+          <t>10,11; 77,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,75; 73,74</t>
+          <t>5,21; 72,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,68; 190,9</t>
+          <t>98,8; 203,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,99</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>7,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,35</t>
+          <t>-0,53; 1,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,03</t>
+          <t>-0,85; 0,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,8</t>
+          <t>3,94; 6,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,54</t>
+          <t>1,84; 4,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,62</t>
+          <t>1,67; 4,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,93; 28,94</t>
+          <t>8,51; 11,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,62</t>
+          <t>0,97; 2,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,48</t>
+          <t>0,81; 2,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,57; 17,29</t>
+          <t>6,55; 8,28</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133,07%</t>
+          <t>145,98%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>208,71%</t>
+          <t>144,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>186,19%</t>
+          <t>145,95%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 45,52</t>
+          <t>-13,54; 45,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 34,15</t>
+          <t>-22,21; 31,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78,94; 196,21</t>
+          <t>100,2; 199,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,54; 75,25</t>
+          <t>24,72; 74,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,98; 74,54</t>
+          <t>22,99; 75,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>128,89; 452,83</t>
+          <t>113,29; 181,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,94; 56,79</t>
+          <t>17,67; 54,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14,34; 51,64</t>
+          <t>14,82; 52,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>126,3; 341,95</t>
+          <t>119,33; 179,06</t>
         </is>
       </c>
     </row>
